--- a/Manuscript_Data/Phosphotriesterase_RFdiffusion3_Science_2026/supplemental_data/supp_data__denovo_PTE_DNA_and_protein_sequences.xlsx
+++ b/Manuscript_Data/Phosphotriesterase_RFdiffusion3_Science_2026/supplemental_data/supp_data__denovo_PTE_DNA_and_protein_sequences.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kinetics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kuncat" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cloning_and_vector" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reproduction_notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'kinetics'!$A$1:$T$20</definedName>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -528,7 +527,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -21743,7 +21741,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Additional tagless comparison; high-[S] detector nonlinearity; see reproduction_notes</t>
+          <t>Additional tagless comparison; high-[S] detector nonlinearity; see analysis_notes</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -22329,11 +22327,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="115" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22351,96 +22349,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tagless provenance</t>
+          <t>Tagless comparison</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Additional comparison from paraoxon_kinetics_FOR_PAPER.ipynb section 11; intentionally outside its original 18-row table and paper figure set.</t>
+          <t>Additional exploratory ZAPP-1 comparison, outside the original 18 paper kinetics entries; not an additional designed hit.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tagless assay</t>
+          <t>Assay</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>260731_p2E3 plate; rows A-F; enzyme columns 9-11; background column 12; 23.4 uM enzyme; 0.3-9.6 mM paraoxon; +25 mM NaHCO3; 300-20000 s (clipped to acquired times).</t>
+          <t>260731_p2E3 plate; rows A-F; enzyme columns 9-11; background column 12; 23.4 uM enzyme; 0.3-9.6 mM paraoxon; +25 mM NaHCO3; 300-20000 s fit window, clipped to acquired times.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tagless protein</t>
+          <t>Protein</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Same designed ZAPP-1 sequence; C-terminal Strep-tag II omitted. Not an additional ordered design. No tagless cloning DNA sequence is inferred.</t>
+          <t>The ZAPP-1 design without its C-terminal Strep-tag II. No tagless cloning DNA sequence is supplied.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tagless uncertainty</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fit SE combined with 6% assumed enzyme-concentration uncertainty and 0.135% calibration uncertainty; shared calibration cancels in kcat/kuncat and (kcat/Km)/kuncat.</t>
+          <t>Fit uncertainty combined with 6% enzyme-concentration uncertainty and 0.135% calibration uncertainty. Calibration cancels in ratios to the condition-matched uncatalyzed rate.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tagless detector check</t>
+          <t>Detector linearity</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>High-[S] traces exceed 2.5 AU. Original side analysis reruns a shorter window; see SIDE__ZAPP1_tagless and notebook output. Do not interpret tiny tagged/tagless differences as a demonstrated effect.</t>
+          <t>High-concentration tagless traces exceed 2.5 AU. The notebook includes a shorter-window sensitivity check; tagged/tagless differences are within the stated uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paper values</t>
+          <t>Figure 4E</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The original 18 kinetics rows and every pre-existing sheet value are unchanged. Raw refits and validation live in wetlab_data_plots/; archived paraoxon_kinetics_ALL_DATA.xlsx retains original rounding and provenance.</t>
+          <t>The original reproduction retains the original no-bicarbonate point calibration; the condition_matched variant uses the no-bicarbonate calibration for points and error bars, consistent with the fitted curve.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Main panel E</t>
+          <t>Mutant labels</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The historical PDF uses the bicarbonate calibration for no-bicarbonate points, unlike its fitted curve. Both the exact historical reproduction and a separately labeled condition-matched correction are generated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mutant labels</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>The archived source workbook describes MUT1-6 -&gt; H93A, H89A, K16A, H170A, H133A, E92A as inferred from motif order; direct sequencing confirmation is not supplied with that workbook.</t>
+          <t>MUT1-6 labels H93A, H89A, K16A, H170A, H133A and E92A follow the reference workbook, which describes this mapping as inferred from motif order without direct sequencing confirmation.</t>
         </is>
       </c>
     </row>
